--- a/static/bw_amr_ig/ValueSet-botswana-amr-antibiotic-susceptibility-loinc.xlsx
+++ b/static/bw_amr_ig/ValueSet-botswana-amr-antibiotic-susceptibility-loinc.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-09T10:14:37-04:00</t>
+    <t>2026-03-13T15:05:11-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/static/bw_amr_ig/ValueSet-botswana-amr-antibiotic-susceptibility-loinc.xlsx
+++ b/static/bw_amr_ig/ValueSet-botswana-amr-antibiotic-susceptibility-loinc.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T15:05:11-04:00</t>
+    <t>2026-03-13T15:54:56-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/static/bw_amr_ig/ValueSet-botswana-amr-antibiotic-susceptibility-loinc.xlsx
+++ b/static/bw_amr_ig/ValueSet-botswana-amr-antibiotic-susceptibility-loinc.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://bw.health.gov/fhir/ImplementationGuide/bw-amr-ig/ValueSet/botswana-amr-antibiotic-susceptibility-loinc</t>
+    <t>http://bw.health.gov/fhir/amr/ValueSet/botswana-amr-antibiotic-susceptibility-loinc</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T15:54:56-04:00</t>
+    <t>2026-03-13T21:27:21-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
